--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128944321</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128944321</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944339</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128944339</v>
+        <v>128944321</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyråsen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335554</v>
+        <v>335670</v>
       </c>
       <c r="R2" t="n">
-        <v>6619468</v>
+        <v>6619558</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -776,56 +784,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128944321</v>
+        <v>128944333</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyråsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335670</v>
+        <v>335545</v>
       </c>
       <c r="R3" t="n">
-        <v>6619558</v>
+        <v>6619426</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +878,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128944339</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stormyråsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>335554</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619468</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128944364</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stormyråsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>335572</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619436</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 14-2024 artfynd.xlsx
+++ b/artfynd/A 14-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944321</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944333</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944339</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>